--- a/قائمة الوحدات الخاصة بالفوج20252026/قائمة جهة نابل فوج قرمبالية المدينة وحدة بلقيس.xlsx
+++ b/قائمة الوحدات الخاصة بالفوج20252026/قائمة جهة نابل فوج قرمبالية المدينة وحدة بلقيس.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="32">
   <si>
     <t>المعرف</t>
   </si>
@@ -104,6 +104,12 @@
   </si>
   <si>
     <t>الحرشاني</t>
+  </si>
+  <si>
+    <t>code_unite</t>
+  </si>
+  <si>
+    <t>LILT</t>
   </si>
 </sst>
 </file>
@@ -485,6 +491,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -511,8 +520,8 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>31</v>
       </c>
       <c r="B2">
         <v>900009451</v>
@@ -540,8 +549,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>31</v>
       </c>
       <c r="B3">
         <v>900007396</v>
@@ -569,8 +578,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
+      <c r="A4" t="s">
+        <v>31</v>
       </c>
       <c r="B4">
         <v>900015513</v>
@@ -598,8 +607,8 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2</v>
+      <c r="A5" t="s">
+        <v>31</v>
       </c>
       <c r="B5">
         <v>900011092</v>
@@ -627,8 +636,8 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>3</v>
+      <c r="A6" t="s">
+        <v>31</v>
       </c>
       <c r="B6">
         <v>900010753</v>
@@ -656,8 +665,8 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>4</v>
+      <c r="A7" t="s">
+        <v>31</v>
       </c>
       <c r="B7">
         <v>900011098</v>
@@ -685,8 +694,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>5</v>
+      <c r="A8" t="s">
+        <v>31</v>
       </c>
       <c r="B8">
         <v>900008061</v>
@@ -714,8 +723,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>6</v>
+      <c r="A9" t="s">
+        <v>31</v>
       </c>
       <c r="B9">
         <v>900011095</v>
@@ -743,8 +752,8 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>7</v>
+      <c r="A10" t="s">
+        <v>31</v>
       </c>
       <c r="B10">
         <v>900013354</v>
@@ -774,7 +783,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1 A2:I3 A4:I10" numberStoredAsText="1"/>
+    <ignoredError sqref="B1:I1 B3:I3 B10:I10 B2:I2 B4:I4 B5:I5 B6:I6 B7:I7 B8:I8 B9:I9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>